--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486792_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486792_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.719200000000001</v>
+        <v>8.0381</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8869</v>
+        <v>5.6528</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8323</v>
+        <v>2.3853</v>
       </c>
       <c r="G2" t="n">
         <v>4.8315</v>
@@ -610,13 +610,13 @@
         <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7292</v>
+        <v>2.0481</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0957</v>
+        <v>0.8616</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6335</v>
+        <v>1.1865</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2037</v>
+        <v>5.6976</v>
       </c>
       <c r="E3" t="n">
-        <v>5.512</v>
+        <v>5.1053</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6917</v>
+        <v>0.5923</v>
       </c>
       <c r="G3" t="n">
         <v>5.5667</v>
@@ -688,13 +688,13 @@
         <v>0.3862</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6716</v>
+        <v>1.1655</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1306</v>
+        <v>0.7238</v>
       </c>
       <c r="U3" t="n">
-        <v>0.541</v>
+        <v>0.4417</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2277</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5383</v>
+        <v>4.2859</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2184</v>
+        <v>2.7424</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3199</v>
+        <v>1.5434</v>
       </c>
       <c r="G4" t="n">
         <v>0.272</v>
@@ -766,13 +766,13 @@
         <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6179</v>
+        <v>1.3654</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0004</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6182</v>
+        <v>0.8417</v>
       </c>
       <c r="V4" t="n">
         <v>2.4554</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9026</v>
+        <v>3.6417</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5052</v>
+        <v>2.443</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3974</v>
+        <v>1.1987</v>
       </c>
       <c r="G5" t="n">
         <v>0.6627</v>
@@ -844,13 +844,13 @@
         <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6953</v>
+        <v>1.4344</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6898</v>
+        <v>0.2479</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3851</v>
+        <v>1.1865</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8174</v>
+        <v>2.1512</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4375</v>
+        <v>1.5479</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3798</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>3.4712</v>
@@ -922,13 +922,13 @@
         <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5626</v>
+        <v>0.8964</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1377</v>
+        <v>0.248</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4249</v>
+        <v>0.6484</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2856</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>I. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6096</v>
+        <v>1.0229</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9181</v>
+        <v>-0.8454</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6915</v>
+        <v>1.8683</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1561</v>
+        <v>0.6988</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3799</v>
+        <v>1.9173</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2239</v>
+        <v>-1.2185</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2675</v>
+        <v>0.4029</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1047</v>
+        <v>1.09</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1628</v>
+        <v>-0.6872</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1115</v>
+        <v>0.2959</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2752</v>
+        <v>0.8272</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3866</v>
+        <v>-0.5313</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.2823</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.0546</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2918</v>
+        <v>0.3242</v>
       </c>
       <c r="T7" t="n">
-        <v>3.0335</v>
+        <v>-0.2829</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2583</v>
+        <v>0.607</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5559</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. MONTERO ISLA</t>
+          <t>H. APARICIO RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6657</v>
+        <v>0.8344</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.004</v>
+        <v>-0.3803</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6697</v>
+        <v>1.2147</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6988</v>
+        <v>-0.0359</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9173</v>
+        <v>0.9656</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2185</v>
+        <v>-1.0015</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4029</v>
+        <v>-0.263</v>
       </c>
       <c r="K8" t="n">
-        <v>1.09</v>
+        <v>0.3451</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6872</v>
+        <v>-0.6081</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2959</v>
+        <v>0.2271</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8272</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5313</v>
+        <v>-0.3934</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0331</v>
+        <v>0.0208</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4415</v>
+        <v>-0.1173</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4083</v>
+        <v>0.1381</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4619</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6247</v>
+        <v>-0.3626</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0865</v>
+        <v>1.0617</v>
       </c>
       <c r="G9" t="n">
         <v>1.6643</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.044</v>
+        <v>0.1932</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2207</v>
+        <v>0.0413</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1768</v>
+        <v>0.1519</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRÍGUEZ</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4275</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5389</v>
+        <v>0.4451</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9664</v>
+        <v>0.2026</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0359</v>
+        <v>0.3511</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9656</v>
+        <v>-0.6279</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0015</v>
+        <v>0.979</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.263</v>
+        <v>-0.2267</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3451</v>
+        <v>-1.1787</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6081</v>
+        <v>0.9519</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2271</v>
+        <v>0.5779</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.5508</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3934</v>
+        <v>0.0271</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.1239</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3862</v>
+        <v>1.262</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2759</v>
+        <v>0.6685</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1102</v>
+        <v>0.5934</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.1271</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6565</v>
+        <v>-2.1271</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. NEGRE FABREGAT</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8679</v>
+        <v>-0.772</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7477</v>
+        <v>-0.9917</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1202</v>
+        <v>0.2197</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3511</v>
+        <v>2.1561</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6279</v>
+        <v>2.3799</v>
       </c>
       <c r="I11" t="n">
-        <v>0.979</v>
+        <v>-0.2239</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2267</v>
+        <v>2.2675</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1787</v>
+        <v>2.1047</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9519</v>
+        <v>0.1628</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5779</v>
+        <v>-0.1115</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5508</v>
+        <v>0.2752</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0271</v>
+        <v>-0.3866</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9654</v>
+        <v>-3.2823</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1239</v>
+        <v>-4.0546</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2537</v>
+        <v>1.9102</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5243</v>
+        <v>1.1236</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2706</v>
+        <v>0.7865</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.5559</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1271</v>
+        <v>-0.3282</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1271</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1729</v>
+        <v>-1.1139</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6574</v>
+        <v>-2.6232</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4845</v>
+        <v>1.5093</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6726</v>
@@ -1390,13 +1390,13 @@
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0443</v>
+        <v>1.1034</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6622</v>
+        <v>0.372</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7065</v>
+        <v>0.7313</v>
       </c>
       <c r="V12" t="n">
         <v>1.2277</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>24.3051</v>
+        <v>25.1327</v>
       </c>
       <c r="E13" t="n">
-        <v>11.9054</v>
+        <v>12.7333</v>
       </c>
       <c r="F13" t="n">
-        <v>12.3995</v>
+        <v>12.3993</v>
       </c>
       <c r="G13" t="n">
-        <v>16.96589999999999</v>
+        <v>16.9659</v>
       </c>
       <c r="H13" t="n">
         <v>23.793</v>
@@ -1447,10 +1447,10 @@
         <v>16.9027</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4188000000000003</v>
+        <v>0.4188000000000005</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3558000000000001</v>
+        <v>-0.3558</v>
       </c>
       <c r="N13" t="n">
         <v>6.890199999999999</v>
@@ -1468,19 +1468,19 @@
         <v>9.654</v>
       </c>
       <c r="S13" t="n">
-        <v>10.8957</v>
+        <v>11.7236</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5827</v>
+        <v>4.4102</v>
       </c>
       <c r="U13" t="n">
-        <v>7.313</v>
+        <v>7.313000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.2704</v>
       </c>
       <c r="W13" t="n">
-        <v>5.482000000000001</v>
+        <v>5.481999999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-4.211600000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. CRUJEIRAS MOREIRAS</t>
+          <t>K. RODRIGUEZ AGUILERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.5243</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3982</v>
+        <v>0.7492</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9774</v>
+        <v>-1.2735</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.037</v>
+        <v>-0.2195</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4966</v>
+        <v>-6.0407</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5403</v>
+        <v>5.8212</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7296</v>
+        <v>2.2926</v>
       </c>
       <c r="K14" t="n">
-        <v>1.297</v>
+        <v>-3.488</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5674</v>
+        <v>5.7806</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7665</v>
+        <v>-2.5121</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7936</v>
+        <v>-2.5527</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0271</v>
+        <v>0.0406</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7723</v>
+        <v>1.5446</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9654</v>
+        <v>2.7031</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3145</v>
+        <v>-1.8068</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1383</v>
+        <v>-1.2418</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1762</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.0426</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. RODRIGUEZ AGUILERA</t>
+          <t>M. CRUJEIRAS MOREIRAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.3602</v>
+        <v>-0.9542</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3355</v>
+        <v>-0.0154</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6956</v>
+        <v>-0.9388</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2195</v>
+        <v>-1.037</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.0407</v>
+        <v>-0.4966</v>
       </c>
       <c r="I15" t="n">
-        <v>5.8212</v>
+        <v>-0.5403</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2926</v>
+        <v>0.7296</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.488</v>
+        <v>1.297</v>
       </c>
       <c r="L15" t="n">
-        <v>5.7806</v>
+        <v>-0.5674</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5121</v>
+        <v>-1.7665</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.5527</v>
+        <v>-1.7936</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0406</v>
+        <v>0.0271</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5446</v>
+        <v>0.7723</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7031</v>
+        <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.6426</v>
+        <v>-0.6896</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.6555</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9872</v>
+        <v>-0.1377</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.0426</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8568</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.9307</v>
+        <v>-1.557</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0799</v>
+        <v>-0.7696</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8508</v>
+        <v>-0.7874</v>
       </c>
       <c r="G16" t="n">
         <v>1.1254</v>
@@ -1702,13 +1702,13 @@
         <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8976</v>
+        <v>-1.5239</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2692</v>
+        <v>-0.9589</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6284</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.4132</v>
+        <v>-2.7676</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3383</v>
+        <v>-0.8554</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0749</v>
+        <v>-1.9121</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0087</v>
@@ -1780,13 +1780,13 @@
         <v>2.3169</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3352</v>
+        <v>-1.6896</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5524</v>
+        <v>-1.0695</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.6201</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2277</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>A. GUERRA LOZANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1418</v>
+        <v>-3.6583</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9074</v>
+        <v>-2.7403</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2343</v>
+        <v>-0.918</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.8119</v>
+        <v>-3.803</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.7034</v>
+        <v>-2.1934</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1084</v>
+        <v>-1.6096</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1622</v>
+        <v>-1.8229</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.7026</v>
+        <v>-0.6067</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5404</v>
+        <v>-1.2162</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6497</v>
+        <v>-1.9801</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0008</v>
+        <v>-1.5867</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6489</v>
+        <v>-0.3934</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1239</v>
+        <v>0.9654</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1239</v>
+        <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2261</v>
+        <v>-0.8207</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7453</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5192</v>
+        <v>-0.0964</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GUERRA LOZANO</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7865</v>
+        <v>-3.7915</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8437</v>
+        <v>-2.0109</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9428</v>
+        <v>-1.7806</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.803</v>
+        <v>-3.8119</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1934</v>
+        <v>-3.7034</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6096</v>
+        <v>-0.1084</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.8229</v>
+        <v>-1.1622</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6067</v>
+        <v>-1.7026</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2162</v>
+        <v>0.5404</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9801</v>
+        <v>-2.6497</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5867</v>
+        <v>-2.0008</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3934</v>
+        <v>-0.6489</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9654</v>
+        <v>2.1239</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1585</v>
+        <v>2.1239</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.949</v>
+        <v>-0.8758</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8277</v>
+        <v>-0.8487</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1212</v>
+        <v>-0.0271</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9049</v>
+        <v>-4.4567</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7836</v>
+        <v>-1.4733</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1213</v>
+        <v>-2.9834</v>
       </c>
       <c r="G20" t="n">
         <v>-4.4678</v>
@@ -2014,13 +2014,13 @@
         <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7654</v>
+        <v>-1.3172</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2692</v>
+        <v>-0.9589</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4962</v>
+        <v>-0.3583</v>
       </c>
       <c r="V20" t="n">
         <v>0.9421</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.1886</v>
+        <v>-5.9058</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.1803</v>
+        <v>-5.2837</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0083</v>
+        <v>-0.6221</v>
       </c>
       <c r="G21" t="n">
         <v>-3.7433</v>
@@ -2092,13 +2092,13 @@
         <v>1.9308</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7655</v>
+        <v>-1.4827</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8556</v>
+        <v>-0.959</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9099</v>
+        <v>-0.5236</v>
       </c>
       <c r="V21" t="n">
         <v>0.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-24.305</v>
+        <v>-23.6154</v>
       </c>
       <c r="E22" t="n">
-        <v>-12.3995</v>
+        <v>-12.3994</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.9054</v>
+        <v>-11.2159</v>
       </c>
       <c r="G22" t="n">
         <v>-16.9658</v>
@@ -2170,13 +2170,13 @@
         <v>14.4809</v>
       </c>
       <c r="S22" t="n">
-        <v>-10.8959</v>
+        <v>-10.2063</v>
       </c>
       <c r="T22" t="n">
-        <v>-7.3132</v>
+        <v>-7.313</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.5827</v>
+        <v>-2.893199999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2703</v>
